--- a/docs/resources/발주서-통일양식-템플릿.xlsx
+++ b/docs/resources/발주서-통일양식-템플릿.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nbcue\OneDrive\문서\Project\MillingLog\milling-log\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D326CD-0F59-4B54-AFF8-6790AA818665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9300BFB4-D2C8-4616-AB4E-68BBEF5F3926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2370" yWindow="810" windowWidth="21870" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="이마트_260819" sheetId="15" r:id="rId1"/>
     <sheet name="택배_260818" sheetId="13" r:id="rId2"/>
-    <sheet name="서울급식_060818" sheetId="12" r:id="rId3"/>
+    <sheet name="서울급식_260818" sheetId="12" r:id="rId3"/>
     <sheet name="해남급식_260821" sheetId="11" r:id="rId4"/>
     <sheet name="시아스_260811" sheetId="14" r:id="rId5"/>
   </sheets>
